--- a/Base/Backlog_41.xlsx
+++ b/Base/Backlog_41.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD9212C-DA05-43EE-899D-03952C4FE800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7F9947-32F3-47F5-BDBA-D9725B18B557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -669,7 +669,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:L42"/>
   <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -802,7 +801,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -837,7 +836,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -872,7 +871,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
@@ -907,7 +906,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -942,7 +941,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
@@ -977,7 +976,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -1012,7 +1011,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -1047,7 +1046,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
@@ -1082,7 +1081,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
@@ -1117,7 +1116,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
@@ -1152,7 +1151,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
@@ -1187,7 +1186,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
@@ -1222,7 +1221,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>11</v>
       </c>
@@ -1295,7 +1294,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>11</v>
       </c>
@@ -1330,7 +1329,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>11</v>
       </c>
@@ -1403,7 +1402,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>11</v>
       </c>
@@ -1438,7 +1437,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>11</v>
       </c>
@@ -1511,7 +1510,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>11</v>
       </c>
@@ -1546,7 +1545,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -1619,7 +1618,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>11</v>
       </c>
@@ -1654,7 +1653,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>11</v>
       </c>
@@ -1689,7 +1688,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>11</v>
       </c>
@@ -1724,7 +1723,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>11</v>
       </c>
@@ -1759,7 +1758,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>11</v>
       </c>
@@ -1794,7 +1793,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>11</v>
       </c>
@@ -1829,7 +1828,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>11</v>
       </c>
@@ -1864,7 +1863,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>11</v>
       </c>
@@ -1932,13 +1931,7 @@
       <c r="I42" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L34" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
-    <filterColumn colId="11">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L34" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1947,7 +1940,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A6A408-5BF6-4E16-8C71-EC6EB1F5A842}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:L22"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2004,7 +1996,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>22</v>
       </c>
@@ -2040,7 +2032,7 @@
       </c>
       <c r="L2" s="18"/>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>22</v>
       </c>
@@ -2076,7 +2068,7 @@
       </c>
       <c r="L3" s="18"/>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
@@ -2112,7 +2104,7 @@
       </c>
       <c r="L4" s="18"/>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
@@ -2148,7 +2140,7 @@
       </c>
       <c r="L5" s="18"/>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
@@ -2184,7 +2176,7 @@
       </c>
       <c r="L6" s="18"/>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
@@ -2220,7 +2212,7 @@
       </c>
       <c r="L7" s="18"/>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>22</v>
       </c>
@@ -2256,7 +2248,7 @@
       </c>
       <c r="L8" s="18"/>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
@@ -2292,7 +2284,7 @@
       </c>
       <c r="L9" s="18"/>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
@@ -2366,7 +2358,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
@@ -2412,13 +2404,7 @@
       <c r="F22" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L12" xr:uid="{16A6A408-5BF6-4E16-8C71-EC6EB1F5A842}">
-    <filterColumn colId="11">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L12" xr:uid="{16A6A408-5BF6-4E16-8C71-EC6EB1F5A842}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
